--- a/Quotation/QU1030524.xlsx
+++ b/Quotation/QU1030524.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{025AB4FB-2129-C241-96C0-DBAE21140045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C458AAAC-9BFF-42BD-8A00-3C1FCED2AA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>Quotation</t>
   </si>
@@ -98,9 +98,18 @@
     <t>Discount (%)</t>
   </si>
   <si>
+    <t>QU1020524</t>
+  </si>
+  <si>
     <t>20/5/2024</t>
   </si>
   <si>
+    <t>Miss Nina - Faster English</t>
+  </si>
+  <si>
+    <t>+6287781080889</t>
+  </si>
+  <si>
     <t>Treehouse 1 - Student Book</t>
   </si>
   <si>
@@ -165,24 +174,6 @@
   </si>
   <si>
     <t>Amount ()</t>
-  </si>
-  <si>
-    <t>Miss Maya - English Private</t>
-  </si>
-  <si>
-    <t>mayaka1503@gmail.com</t>
-  </si>
-  <si>
-    <t>081932390900</t>
-  </si>
-  <si>
-    <t>QU1030524</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Jumlah</t>
   </si>
 </sst>
 </file>
@@ -222,6 +213,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="6"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
@@ -239,14 +235,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -259,8 +249,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -397,101 +393,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF505050"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF505050"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF505050"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF505050"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF505050"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF505050"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF505050"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF505050"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -577,41 +483,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -619,45 +498,44 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1009,28 +887,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.609375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="98.3359375" style="11" customWidth="1"/>
-    <col min="3" max="3" width="25.01953125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.71875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.953125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="20.71484375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="40.48828125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.71875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="98.28515625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="40.42578125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E1" s="2"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E2" s="2"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:8" s="4" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A3" s="3"/>
       <c r="B3" s="12" t="s">
         <v>0</v>
@@ -1042,98 +920,96 @@
       <c r="G3" s="8"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D5" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42" t="s">
+      <c r="C6" s="33"/>
+      <c r="D6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="42" t="s">
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42" t="s">
+      <c r="C9" s="33"/>
+      <c r="D9" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="42" t="s">
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C11" s="33"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>14</v>
       </c>
@@ -1147,8 +1023,11 @@
       <c r="F14" s="23"/>
       <c r="G14" s="23"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="31"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="31">
+        <f>SUM(G18:G37)</f>
+        <v>2355200</v>
+      </c>
       <c r="C15" s="9">
         <v>20</v>
       </c>
@@ -1156,7 +1035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
         <v>17</v>
       </c>
@@ -1167,496 +1046,505 @@
         <v>19</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="49" t="s">
+      <c r="G17" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="40">
+        <v>9781613527948</v>
+      </c>
+      <c r="D18" s="39">
+        <v>1</v>
+      </c>
+      <c r="E18" s="41">
+        <v>189000</v>
+      </c>
+      <c r="F18" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="41">
+        <v>151200</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="40">
+        <v>9781613527962</v>
+      </c>
+      <c r="D19" s="39">
+        <v>1</v>
+      </c>
+      <c r="E19" s="41">
+        <v>189000</v>
+      </c>
+      <c r="F19" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G19" s="41">
+        <v>151200</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="40">
+        <v>9781613527986</v>
+      </c>
+      <c r="D20" s="39">
+        <v>1</v>
+      </c>
+      <c r="E20" s="41">
+        <v>189000</v>
+      </c>
+      <c r="F20" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G20" s="41">
+        <v>151200</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="40">
+        <v>9781685912758</v>
+      </c>
+      <c r="D21" s="39">
+        <v>1</v>
+      </c>
+      <c r="E21" s="41">
+        <v>140000</v>
+      </c>
+      <c r="F21" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="41">
+        <v>112000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="40">
+        <v>9781685912772</v>
+      </c>
+      <c r="D22" s="39">
+        <v>1</v>
+      </c>
+      <c r="E22" s="41">
+        <v>140000</v>
+      </c>
+      <c r="F22" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G22" s="41">
+        <v>112000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="40">
+        <v>9781685912796</v>
+      </c>
+      <c r="D23" s="39">
+        <v>1</v>
+      </c>
+      <c r="E23" s="41">
+        <v>140000</v>
+      </c>
+      <c r="F23" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G23" s="41">
+        <v>112000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="40">
+        <v>9781685912819</v>
+      </c>
+      <c r="D24" s="39">
+        <v>1</v>
+      </c>
+      <c r="E24" s="41">
+        <v>140000</v>
+      </c>
+      <c r="F24" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G24" s="41">
+        <v>112000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="40">
+        <v>9781685912833</v>
+      </c>
+      <c r="D25" s="39">
+        <v>1</v>
+      </c>
+      <c r="E25" s="41">
+        <v>140000</v>
+      </c>
+      <c r="F25" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G25" s="41">
+        <v>112000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="40">
+        <v>9781685914448</v>
+      </c>
+      <c r="D26" s="39">
+        <v>1</v>
+      </c>
+      <c r="E26" s="41">
+        <v>140000</v>
+      </c>
+      <c r="F26" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G26" s="41">
+        <v>112000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="40">
+        <v>9781640157378</v>
+      </c>
+      <c r="D27" s="39">
+        <v>1</v>
+      </c>
+      <c r="E27" s="41">
+        <v>152000</v>
+      </c>
+      <c r="F27" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G27" s="41">
+        <v>121600</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="40">
+        <v>9781640157385</v>
+      </c>
+      <c r="D28" s="39">
+        <v>1</v>
+      </c>
+      <c r="E28" s="41">
+        <v>152000</v>
+      </c>
+      <c r="F28" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G28" s="41">
+        <v>121600</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="40">
+        <v>9781640157392</v>
+      </c>
+      <c r="D29" s="39">
+        <v>1</v>
+      </c>
+      <c r="E29" s="41">
+        <v>152000</v>
+      </c>
+      <c r="F29" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G29" s="41">
+        <v>121600</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="40">
+        <v>9781640155978</v>
+      </c>
+      <c r="D30" s="39">
+        <v>1</v>
+      </c>
+      <c r="E30" s="41">
+        <v>125000</v>
+      </c>
+      <c r="F30" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G30" s="41">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="40">
+        <v>9781640155985</v>
+      </c>
+      <c r="D31" s="39">
+        <v>1</v>
+      </c>
+      <c r="E31" s="41">
+        <v>125000</v>
+      </c>
+      <c r="F31" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G31" s="41">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="40">
+        <v>9781640155992</v>
+      </c>
+      <c r="D32" s="39">
+        <v>1</v>
+      </c>
+      <c r="E32" s="41">
+        <v>125000</v>
+      </c>
+      <c r="F32" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G32" s="41">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="40">
+        <v>9781640156005</v>
+      </c>
+      <c r="D33" s="39">
+        <v>1</v>
+      </c>
+      <c r="E33" s="41">
+        <v>125000</v>
+      </c>
+      <c r="F33" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G33" s="41">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="40">
+        <v>9781640156012</v>
+      </c>
+      <c r="D34" s="39">
+        <v>1</v>
+      </c>
+      <c r="E34" s="41">
+        <v>125000</v>
+      </c>
+      <c r="F34" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="41">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="40">
+        <v>9781640158757</v>
+      </c>
+      <c r="D35" s="39">
+        <v>1</v>
+      </c>
+      <c r="E35" s="41">
+        <v>152000</v>
+      </c>
+      <c r="F35" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G35" s="41">
+        <v>121600</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="54" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="34">
-        <v>9781613527948</v>
-      </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="35">
-        <v>189000</v>
-      </c>
-      <c r="F18" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G18" s="50">
-        <v>151200</v>
-      </c>
-      <c r="H18" s="48"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B19" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="34">
-        <v>9781613527962</v>
-      </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="35">
-        <v>189000</v>
-      </c>
-      <c r="F19" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G19" s="50">
-        <v>151200</v>
-      </c>
-      <c r="H19" s="48"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="34">
-        <v>9781613527986</v>
-      </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="35">
-        <v>189000</v>
-      </c>
-      <c r="F20" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G20" s="50">
-        <v>151200</v>
-      </c>
-      <c r="H20" s="48"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="34">
-        <v>9781685912758</v>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="35">
-        <v>140000</v>
-      </c>
-      <c r="F21" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G21" s="50">
-        <v>112000</v>
-      </c>
-      <c r="H21" s="48"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="34">
-        <v>9781685912772</v>
-      </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="35">
-        <v>140000</v>
-      </c>
-      <c r="F22" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G22" s="50">
-        <v>112000</v>
-      </c>
-      <c r="H22" s="48"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="34">
-        <v>9781685912796</v>
-      </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="35">
-        <v>140000</v>
-      </c>
-      <c r="F23" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G23" s="50">
-        <v>112000</v>
-      </c>
-      <c r="H23" s="48"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="34">
-        <v>9781685912819</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="35">
-        <v>140000</v>
-      </c>
-      <c r="F24" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G24" s="50">
-        <v>112000</v>
-      </c>
-      <c r="H24" s="48"/>
-    </row>
-    <row r="25" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="34">
-        <v>9781685912833</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="35">
-        <v>140000</v>
-      </c>
-      <c r="F25" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G25" s="50">
-        <v>112000</v>
-      </c>
-      <c r="H25" s="48"/>
-    </row>
-    <row r="26" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="34">
-        <v>9781685914448</v>
-      </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="35">
-        <v>140000</v>
-      </c>
-      <c r="F26" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G26" s="50">
-        <v>112000</v>
-      </c>
-      <c r="H26" s="48"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="34">
-        <v>9781640157378</v>
-      </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="35">
+      <c r="C36" s="40">
+        <v>9781640158764</v>
+      </c>
+      <c r="D36" s="39">
+        <v>1</v>
+      </c>
+      <c r="E36" s="41">
         <v>152000</v>
       </c>
-      <c r="F27" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G27" s="50">
+      <c r="F36" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="G36" s="41">
         <v>121600</v>
       </c>
-      <c r="H27" s="48"/>
-    </row>
-    <row r="28" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="34">
-        <v>9781640157385</v>
-      </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="35">
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="44">
+        <v>9781640158771</v>
+      </c>
+      <c r="D37" s="43">
+        <v>1</v>
+      </c>
+      <c r="E37" s="41">
         <v>152000</v>
       </c>
-      <c r="F28" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G28" s="50">
+      <c r="F37" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="G37" s="41">
         <v>121600</v>
       </c>
-      <c r="H28" s="48"/>
-    </row>
-    <row r="29" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="34">
-        <v>9781640157392</v>
-      </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="35">
-        <v>152000</v>
-      </c>
-      <c r="F29" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G29" s="50">
-        <v>121600</v>
-      </c>
-      <c r="H29" s="48"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="34">
-        <v>9781640155978</v>
-      </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="35">
-        <v>125000</v>
-      </c>
-      <c r="F30" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G30" s="50">
-        <v>100000</v>
-      </c>
-      <c r="H30" s="48"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="34">
-        <v>9781640155985</v>
-      </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="35">
-        <v>125000</v>
-      </c>
-      <c r="F31" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G31" s="50">
-        <v>100000</v>
-      </c>
-      <c r="H31" s="48"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="34">
-        <v>9781640155992</v>
-      </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="35">
-        <v>125000</v>
-      </c>
-      <c r="F32" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G32" s="50">
-        <v>100000</v>
-      </c>
-      <c r="H32" s="48"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="34">
-        <v>9781640156005</v>
-      </c>
-      <c r="D33" s="33"/>
-      <c r="E33" s="35">
-        <v>125000</v>
-      </c>
-      <c r="F33" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G33" s="50">
-        <v>100000</v>
-      </c>
-      <c r="H33" s="48"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="34">
-        <v>9781640156012</v>
-      </c>
-      <c r="D34" s="33"/>
-      <c r="E34" s="35">
-        <v>125000</v>
-      </c>
-      <c r="F34" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G34" s="50">
-        <v>100000</v>
-      </c>
-      <c r="H34" s="48"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="34">
-        <v>9781640158757</v>
-      </c>
-      <c r="D35" s="33"/>
-      <c r="E35" s="35">
-        <v>152000</v>
-      </c>
-      <c r="F35" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G35" s="50">
-        <v>121600</v>
-      </c>
-      <c r="H35" s="48"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="34">
-        <v>9781640158764</v>
-      </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="35">
-        <v>152000</v>
-      </c>
-      <c r="F36" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="G36" s="50">
-        <v>121600</v>
-      </c>
-      <c r="H36" s="48"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="38">
-        <v>9781640158771</v>
-      </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40">
-        <v>152000</v>
-      </c>
-      <c r="F37" s="46">
-        <v>0.2</v>
-      </c>
-      <c r="G37" s="51">
-        <v>121600</v>
-      </c>
-      <c r="H37" s="48"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F38" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="G38" s="52"/>
-      <c r="H38" s="53"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="25" t="s">
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="27"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B41" s="16"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="27"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="16"/>
+      <c r="E40" s="2"/>
+      <c r="G40" s="17"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="16" t="s">
+        <v>9</v>
+      </c>
       <c r="E41" s="2"/>
       <c r="G41" s="17"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" s="2"/>
       <c r="G42" s="17"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43" s="2"/>
       <c r="G43" s="17"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
-        <v>11</v>
-      </c>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="16"/>
       <c r="E44" s="2"/>
       <c r="G44" s="17"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="16"/>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="18" t="s">
+        <v>12</v>
+      </c>
       <c r="E45" s="2"/>
       <c r="G45" s="17"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="G46" s="17"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="16"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="19"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="16" t="s">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="16"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="19"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="16" t="s">
         <v>13</v>
       </c>
+      <c r="E47" s="2"/>
+      <c r="G47" s="17"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="16"/>
       <c r="E48" s="2"/>
       <c r="G48" s="17"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="16"/>
       <c r="E49" s="2"/>
       <c r="G49" s="17"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="16"/>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="29" t="s">
+        <v>23</v>
+      </c>
       <c r="E50" s="2"/>
       <c r="G50" s="17"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="G51" s="17"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B52" s="20"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="22"/>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="20"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="G38:H38"/>
+  <mergeCells count="10">
     <mergeCell ref="D10:G12"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="D7:G8"/>
@@ -1668,12 +1556,9 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B7:C8"/>
   </mergeCells>
-  <phoneticPr fontId="5" alignment="center"/>
-  <hyperlinks>
-    <hyperlink ref="B10:C10" r:id="rId1" xr:uid="{82B0550C-424D-8341-9755-E82A48CD1440}"/>
-  </hyperlinks>
+  <phoneticPr fontId="6" alignment="center"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>